--- a/etf_holdings/2026-09-15_common_holdings_all.xlsx
+++ b/etf_holdings/2026-09-15_common_holdings_all.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>10.18%</t>
+          <t>10.42%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -662,7 +662,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>11.79%</t>
+          <t>12.05%</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -675,7 +675,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>9.45%</t>
+          <t>9.42%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -701,7 +701,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>15.36%</t>
+          <t>15.71%</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -714,7 +714,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>14.87%</t>
+          <t>14.79%</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -753,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.66%</t>
         </is>
       </c>
       <c r="AD2" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>9.21%</t>
+          <t>9.47%</t>
         </is>
       </c>
       <c r="AG2" t="n">
@@ -792,7 +792,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>8.79%</t>
+          <t>9.02%</t>
         </is>
       </c>
       <c r="AM2" t="n">
@@ -800,12 +800,12 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>107.46%</t>
+          <t>108.75%</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>8.95%</t>
+          <t>9.06%</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8.53%</t>
+          <t>8.46%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -848,7 +848,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5.94%</t>
+          <t>5.89%</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -861,7 +861,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>5.95%</t>
+          <t>5.97%</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -887,7 +887,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>6.64%</t>
+          <t>6.58%</t>
         </is>
       </c>
       <c r="R3" t="n">
@@ -939,7 +939,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>8.24%</t>
+          <t>8.28%</t>
         </is>
       </c>
       <c r="AD3" t="n">
@@ -952,7 +952,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>5.72%</t>
+          <t>5.70%</t>
         </is>
       </c>
       <c r="AG3" t="n">
@@ -978,7 +978,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>7.65%</t>
+          <t>7.62%</t>
         </is>
       </c>
       <c r="AM3" t="n">
@@ -986,12 +986,12 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>69.42%</t>
+          <t>69.25%</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>5.79%</t>
+          <t>5.77%</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9.15%</t>
+          <t>8.95%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>9.62%</t>
+          <t>9.38%</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>3.80%</t>
+          <t>3.82%</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>5.63%</t>
+          <t>5.50%</t>
         </is>
       </c>
       <c r="R4" t="n">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.71%</t>
         </is>
       </c>
       <c r="U4" t="n">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>4.27%</t>
+          <t>4.22%</t>
         </is>
       </c>
       <c r="AD4" t="n">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>5.61%</t>
+          <t>5.51%</t>
         </is>
       </c>
       <c r="AG4" t="n">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.25%</t>
         </is>
       </c>
       <c r="AM4" t="n">
@@ -1172,12 +1172,12 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>63.25%</t>
+          <t>62.48%</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>5.27%</t>
+          <t>5.21%</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>7.10%</t>
+          <t>6.82%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5.39%</t>
+          <t>5.18%</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.33%</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>6.21%</t>
+          <t>5.97%</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.68%</t>
         </is>
       </c>
       <c r="U5" t="n">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>4.71%</t>
+          <t>4.58%</t>
         </is>
       </c>
       <c r="AD5" t="n">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>5.80%</t>
+          <t>5.59%</t>
         </is>
       </c>
       <c r="AG5" t="n">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>4.46%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="AM5" t="n">
@@ -1358,12 +1358,12 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>53.51%</t>
+          <t>52.24%</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>4.46%</t>
+          <t>4.35%</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
